--- a/templates/xlsx/selling-points.xlsx
+++ b/templates/xlsx/selling-points.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selling-Point Sprint" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="About" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>

--- a/templates/xlsx/selling-points.xlsx
+++ b/templates/xlsx/selling-points.xlsx
@@ -1813,7 +1813,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>List every possible selling point, grade it, test two per week through creators and own content, then go all-in on the proven one.</t>
+          <t>List every selling point and grade it S/A/B/C (CC's slide). Rotate ONE selling point per test week (CC: week 1 point A, week 2 B, week 3 C …); CC also describes running two per week when capacity allows. Aggregate the data, then go all-in on the proven one.</t>
         </is>
       </c>
     </row>
